--- a/data/trans_orig/P02E$contratada-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007 (tasa de respuesta: 96,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105251</t>
+          <t>104701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121124</t>
+          <t>121016</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185980</t>
+          <t>187579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205250</t>
+          <t>205673</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297948</t>
+          <t>297115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>323075</t>
+          <t>322336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23103</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27814</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46670</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>21666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169322</t>
+          <t>169128</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>186432</t>
+          <t>185953</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>267116</t>
+          <t>265512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>287583</t>
+          <t>287520</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443531</t>
+          <t>443569</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>469823</t>
+          <t>470003</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29620</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>22818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1527,97 +1527,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106287</t>
+          <t>106692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120575</t>
+          <t>120830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169365</t>
+          <t>169985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185616</t>
+          <t>186094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>280847</t>
+          <t>281097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302364</t>
+          <t>301835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>6908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>21046</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8779</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>19746</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1983,97 +1983,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4437</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>897</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>5033</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1656</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144331</t>
+          <t>145560</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159104</t>
+          <t>159829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>256815</t>
+          <t>257601</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>274076</t>
+          <t>274169</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410402</t>
+          <t>410482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>431831</t>
+          <t>430934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29672</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7469</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28288</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>41571</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>546033</t>
+          <t>542866</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>577409</t>
+          <t>575356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>902148</t>
+          <t>904399</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>938991</t>
+          <t>938538</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1458464</t>
+          <t>1459284</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1506307</t>
+          <t>1507798</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46801</t>
+          <t>48783</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77212</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93071</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134732</t>
+          <t>134030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13372</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172815</t>
+          <t>172435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189275</t>
+          <t>189658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255872</t>
+          <t>255954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276777</t>
+          <t>277056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>434169</t>
+          <t>435429</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>461638</t>
+          <t>461893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,9%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>19058</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>43475</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10585</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17147</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>13243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15811</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>272437</t>
+          <t>273439</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>290195</t>
+          <t>290317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>405078</t>
+          <t>405380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>430137</t>
+          <t>430082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>685913</t>
+          <t>684084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>715383</t>
+          <t>715425</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17664</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38397</t>
+          <t>38253</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>26422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52691</t>
+          <t>51583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15388</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>22028</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12653</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193381</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210199</t>
+          <t>210400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>322948</t>
+          <t>323022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>341124</t>
+          <t>341441</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>522105</t>
+          <t>523180</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>548129</t>
+          <t>547660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22269</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>34896</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22073</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219944</t>
+          <t>219092</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241333</t>
+          <t>241135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357439</t>
+          <t>356019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379966</t>
+          <t>380543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>584567</t>
+          <t>584856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>615308</t>
+          <t>617106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28899</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26912</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50627</t>
+          <t>53190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42096</t>
+          <t>41051</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>33115</t>
+          <t>32835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>61688</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>881615</t>
+          <t>880605</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>916099</t>
+          <t>917356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1366090</t>
+          <t>1367614</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1411974</t>
+          <t>1410901</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2260750</t>
+          <t>2263198</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2318630</t>
+          <t>2319630</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,72%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>63294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100977</t>
+          <t>98066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>109007</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158601</t>
+          <t>156063</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29755</t>
+          <t>30853</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25836</t>
+          <t>25363</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>50094</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016 (tasa de respuesta: 93,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131405</t>
+          <t>131693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147665</t>
+          <t>148188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167098</t>
+          <t>169260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184852</t>
+          <t>184330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304618</t>
+          <t>305287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>327903</t>
+          <t>328842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25877</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8840</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,47 +6262,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>8068</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3435</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>17181</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>8068</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>16647</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217548</t>
+          <t>217236</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>231295</t>
+          <t>231269</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>302817</t>
+          <t>303179</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>328485</t>
+          <t>329173</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>526162</t>
+          <t>526769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>555125</t>
+          <t>555101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>44319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>28914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>53963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>17158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142443</t>
+          <t>142778</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156887</t>
+          <t>156912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213584</t>
+          <t>212193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234084</t>
+          <t>234151</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363232</t>
+          <t>362297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>388259</t>
+          <t>387760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>33874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>41739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8159</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23739</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165237</t>
+          <t>165093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182158</t>
+          <t>182083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>238752</t>
+          <t>240128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>266873</t>
+          <t>265757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>411043</t>
+          <t>412640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>443224</t>
+          <t>442540</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48974</t>
+          <t>47622</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64310</t>
+          <t>64355</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27925</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29124</t>
+          <t>30033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54874</t>
+          <t>55725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>675488</t>
+          <t>675867</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>705880</t>
+          <t>707739</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>950221</t>
+          <t>951264</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>995994</t>
+          <t>995468</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1638097</t>
+          <t>1636825</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1689040</t>
+          <t>1689541</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27861</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>52759</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85700</t>
+          <t>86790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126184</t>
+          <t>125425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>121619</t>
+          <t>122174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>169745</t>
+          <t>171046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18585</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>19067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>32176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P02E$contratada-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>11152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104701</t>
+          <t>104755</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121016</t>
+          <t>120728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187579</t>
+          <t>186320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205673</t>
+          <t>205159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>297115</t>
+          <t>298585</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322336</t>
+          <t>321811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>22965</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>43745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12389</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21666</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169128</t>
+          <t>168100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>185953</t>
+          <t>186040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>265512</t>
+          <t>267278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>287520</t>
+          <t>287552</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443569</t>
+          <t>443259</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>470003</t>
+          <t>469615</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21717</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>44739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>970</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106692</t>
+          <t>106846</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120830</t>
+          <t>120787</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169985</t>
+          <t>169505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186094</t>
+          <t>186292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>281097</t>
+          <t>281379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301835</t>
+          <t>303079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>20892</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>18589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145560</t>
+          <t>145309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159829</t>
+          <t>160374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>257601</t>
+          <t>258704</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>274169</t>
+          <t>274269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410482</t>
+          <t>408791</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>430934</t>
+          <t>430778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14650</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>28466</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>9967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41571</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>542866</t>
+          <t>545566</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>575356</t>
+          <t>576200</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>904399</t>
+          <t>903129</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>938538</t>
+          <t>938878</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1459284</t>
+          <t>1458314</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1507798</t>
+          <t>1506480</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48783</t>
+          <t>48958</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77764</t>
+          <t>79429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92870</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134030</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2875</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13015</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172435</t>
+          <t>172210</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189658</t>
+          <t>189827</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>253838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277056</t>
+          <t>276396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>435429</t>
+          <t>435430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>461893</t>
+          <t>461478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>17454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>31811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -3583,12 +3583,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3598,12 +3598,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17205</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>273439</t>
+          <t>271161</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>290317</t>
+          <t>290236</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>405380</t>
+          <t>405589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>430082</t>
+          <t>430457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>684084</t>
+          <t>687127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>715425</t>
+          <t>716285</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38253</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26422</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51583</t>
+          <t>52637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>15356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>20528</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194422</t>
+          <t>193928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210400</t>
+          <t>210338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323022</t>
+          <t>323288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>341441</t>
+          <t>341511</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>523180</t>
+          <t>521993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>547660</t>
+          <t>547685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22947</t>
+          <t>22079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15060</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34896</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>7082</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>29970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219092</t>
+          <t>219892</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241135</t>
+          <t>241087</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>356019</t>
+          <t>358567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380543</t>
+          <t>381760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>584856</t>
+          <t>584653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617106</t>
+          <t>617051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30042</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>29290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>27880</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53190</t>
+          <t>51558</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4951,12 +4951,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>41013</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>61688</t>
+          <t>61828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>880605</t>
+          <t>881128</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>917356</t>
+          <t>917470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1367614</t>
+          <t>1366515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1410901</t>
+          <t>1409518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2263198</t>
+          <t>2259547</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2319630</t>
+          <t>2316987</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63294</t>
+          <t>63874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98066</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109007</t>
+          <t>111033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>156063</t>
+          <t>156376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -5407,12 +5407,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30853</t>
+          <t>29190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50094</t>
+          <t>49172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131693</t>
+          <t>130507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148188</t>
+          <t>147282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>169260</t>
+          <t>168582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184330</t>
+          <t>184802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305287</t>
+          <t>305660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>328842</t>
+          <t>328489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>8990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>35901</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6198</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217236</t>
+          <t>215341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>231269</t>
+          <t>230905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>303179</t>
+          <t>304146</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>329173</t>
+          <t>328660</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>526769</t>
+          <t>527407</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>555101</t>
+          <t>555344</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22165</t>
+          <t>22208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>44043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28914</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53963</t>
+          <t>53481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142778</t>
+          <t>141844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>156912</t>
+          <t>156382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>212193</t>
+          <t>214045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234151</t>
+          <t>233787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>362297</t>
+          <t>362231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387760</t>
+          <t>387473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>14622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33874</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>41739</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16310</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8355</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23161</t>
+          <t>23333</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165093</t>
+          <t>165270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182083</t>
+          <t>182569</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240128</t>
+          <t>239564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>265757</t>
+          <t>265673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412640</t>
+          <t>413335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>442540</t>
+          <t>444086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21628</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47622</t>
+          <t>47670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>36316</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64355</t>
+          <t>63276</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7548,12 +7548,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>27798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>33511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55725</t>
+          <t>54461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>675867</t>
+          <t>674813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>707739</t>
+          <t>705713</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>950051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>995468</t>
+          <t>994923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1636825</t>
+          <t>1636538</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1689541</t>
+          <t>1691819</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>28249</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52759</t>
+          <t>52097</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86790</t>
+          <t>85011</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125425</t>
+          <t>125404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122174</t>
+          <t>122813</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171046</t>
+          <t>167237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19067</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7989,12 +7989,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13685</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32692</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
